--- a/data/performance/daily/signal_list_2026-05-18.xlsx
+++ b/data/performance/daily/signal_list_2026-05-18.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 22.6%  (7W / 24L of 31 evaluated)</t>
+          <t>Win Rate: 16.1%  (5W / 26L of 31 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2670</v>
+        <v>2630</v>
       </c>
       <c r="D5" t="n">
         <v>2580</v>
@@ -553,10 +553,10 @@
         <v>2670</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-3.37</v>
+        <v>-1.9</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="D7" t="n">
         <v>2240</v>
@@ -637,10 +637,10 @@
         <v>2460</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.03</v>
+        <v>6.49</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.45</v>
+        <v>-3.03</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
         <v>338</v>
@@ -679,10 +679,10 @@
         <v>350</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.74</v>
+        <v>-1.17</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1215</v>
+        <v>1200</v>
       </c>
       <c r="D12" t="n">
         <v>1175</v>
@@ -847,10 +847,10 @@
         <v>1225</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.82</v>
+        <v>2.08</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.29</v>
+        <v>-2.08</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2600</v>
+        <v>2890</v>
       </c>
       <c r="D13" t="n">
         <v>3130</v>
@@ -889,10 +889,10 @@
         <v>3600</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>38.46</v>
+        <v>24.57</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>20.38</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5900</v>
+        <v>5925</v>
       </c>
       <c r="D15" t="n">
         <v>5925</v>
@@ -973,14 +973,14 @@
         <v>6125</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.81</v>
+        <v>3.38</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D16" t="n">
         <v>995</v>
@@ -1015,10 +1015,10 @@
         <v>1010</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.49</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1725</v>
+        <v>1720</v>
       </c>
       <c r="D17" t="n">
         <v>1710</v>
@@ -1057,10 +1057,10 @@
         <v>1730</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.87</v>
+        <v>-0.58</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2680</v>
+        <v>2670</v>
       </c>
       <c r="D20" t="n">
         <v>2600</v>
@@ -1183,10 +1183,10 @@
         <v>2720</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.99</v>
+        <v>-2.62</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>761.73</v>
+        <v>850</v>
       </c>
       <c r="D21" t="n">
         <v>735</v>
@@ -1225,10 +1225,10 @@
         <v>761.73</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0</v>
+        <v>-10.39</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.51</v>
+        <v>-13.53</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6750</v>
+        <v>6575</v>
       </c>
       <c r="D22" t="n">
         <v>5950</v>
@@ -1267,10 +1267,10 @@
         <v>6775</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.37</v>
+        <v>3.04</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-11.85</v>
+        <v>-9.51</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1765</v>
+        <v>1800</v>
       </c>
       <c r="D24" t="n">
         <v>1770</v>
@@ -1351,14 +1351,14 @@
         <v>1795</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.7</v>
+        <v>-0.28</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.67</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="D25" t="n">
         <v>855</v>
@@ -1393,10 +1393,10 @@
         <v>950</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-10</v>
+        <v>-9.52</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D26" t="n">
         <v>234</v>
@@ -1435,10 +1435,10 @@
         <v>252</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.14</v>
+        <v>-2.5</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D27" t="n">
         <v>218</v>
@@ -1477,10 +1477,10 @@
         <v>234</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.54</v>
+        <v>4.46</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.54</v>
+        <v>-2.68</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D28" t="n">
         <v>426</v>
@@ -1519,10 +1519,10 @@
         <v>434</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.84</v>
+        <v>3.33</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.95</v>
+        <v>1.43</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="D30" t="n">
         <v>1010</v>
@@ -1603,10 +1603,10 @@
         <v>1030</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3</v>
+        <v>4.57</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>2.54</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D33" t="n">
         <v>432</v>
@@ -1729,10 +1729,10 @@
         <v>500</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-13.6</v>
+        <v>-12.55</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-18.xlsx
+++ b/data/performance/daily/signal_list_2026-05-18.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-18.xlsx
+++ b/data/performance/daily/signal_list_2026-05-18.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-18.xlsx
+++ b/data/performance/daily/signal_list_2026-05-18.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J252"/>
+  <dimension ref="A1:K252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -857,12 +898,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -894,17 +940,22 @@
       <c r="G13" s="4" t="n">
         <v>-1.26</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -941,12 +992,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -983,12 +1039,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1020,17 +1081,22 @@
       <c r="G16" s="4" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1067,12 +1133,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1109,12 +1180,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1146,17 +1222,22 @@
       <c r="G19" s="4" t="n">
         <v>-3.95</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1188,17 +1269,22 @@
       <c r="G20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1235,12 +1321,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1272,17 +1363,22 @@
       <c r="G22" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1319,12 +1415,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,17 +1457,22 @@
       <c r="G24" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,12 +1509,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1445,12 +1556,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1487,12 +1603,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1571,12 +1697,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1608,17 +1739,22 @@
       <c r="G30" s="4" t="n">
         <v>-1.46</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1655,12 +1791,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1692,17 +1833,22 @@
       <c r="G32" s="4" t="n">
         <v>-3.48</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1739,12 +1885,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1781,12 +1932,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1823,12 +1979,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1865,12 +2026,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1902,17 +2068,22 @@
       <c r="G37" s="4" t="n">
         <v>-0.83</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1949,12 +2120,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1991,12 +2167,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2033,12 +2214,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2075,12 +2261,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2117,12 +2308,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2159,12 +2355,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2201,12 +2402,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2238,17 +2444,22 @@
       <c r="G45" s="4" t="n">
         <v>-3.94</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2285,12 +2496,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2322,17 +2538,22 @@
       <c r="G47" s="4" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2369,12 +2590,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2411,12 +2637,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2453,12 +2684,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2495,12 +2731,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2537,12 +2778,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2574,17 +2820,22 @@
       <c r="G53" s="4" t="n">
         <v>-2.47</v>
       </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,12 +2872,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2658,17 +2914,22 @@
       <c r="G55" s="4" t="n">
         <v>-6.47</v>
       </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2700,17 +2961,22 @@
       <c r="G56" s="4" t="n">
         <v>-6.55</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2747,12 +3013,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2789,12 +3060,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2831,12 +3107,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2868,17 +3149,22 @@
       <c r="G60" s="4" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2910,17 +3196,22 @@
       <c r="G61" s="4" t="n">
         <v>-5.41</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2957,12 +3248,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2999,12 +3295,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3041,12 +3342,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3078,17 +3384,22 @@
       <c r="G65" s="4" t="n">
         <v>-2.34</v>
       </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3125,12 +3436,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3167,12 +3483,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3204,17 +3525,22 @@
       <c r="G68" s="4" t="n">
         <v>-4.05</v>
       </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3251,12 +3577,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3293,12 +3624,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3335,12 +3671,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3372,17 +3713,22 @@
       <c r="G72" s="4" t="n">
         <v>-0.52</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3419,12 +3765,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3461,12 +3812,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3498,17 +3854,22 @@
       <c r="G75" s="4" t="n">
         <v>-10.88</v>
       </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3540,17 +3901,22 @@
       <c r="G76" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3587,12 +3953,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3624,17 +3995,22 @@
       <c r="G78" s="4" t="n">
         <v>-3.06</v>
       </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3671,12 +4047,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3713,12 +4094,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3750,17 +4136,22 @@
       <c r="G81" s="4" t="n">
         <v>-1.88</v>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3797,12 +4188,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3834,17 +4230,22 @@
       <c r="G83" s="4" t="n">
         <v>-4.21</v>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3881,12 +4282,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3923,12 +4329,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3965,12 +4376,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4007,12 +4423,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4044,17 +4465,22 @@
       <c r="G88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4091,12 +4517,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4133,12 +4564,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4170,17 +4606,22 @@
       <c r="G91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4217,12 +4658,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4259,12 +4705,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4296,17 +4747,22 @@
       <c r="G94" s="4" t="n">
         <v>-0.96</v>
       </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4338,17 +4794,22 @@
       <c r="G95" s="4" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4385,12 +4846,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4422,17 +4888,22 @@
       <c r="G97" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4469,12 +4940,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4511,12 +4987,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4553,12 +5034,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4590,17 +5076,22 @@
       <c r="G101" s="4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4637,12 +5128,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4674,17 +5170,22 @@
       <c r="G103" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4721,12 +5222,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4763,12 +5269,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4805,12 +5316,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4842,17 +5358,22 @@
       <c r="G107" s="4" t="n">
         <v>-1.26</v>
       </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4889,12 +5410,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4931,12 +5457,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4973,12 +5504,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5010,17 +5546,22 @@
       <c r="G111" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5057,12 +5598,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5094,17 +5640,22 @@
       <c r="G113" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5141,12 +5692,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5183,12 +5739,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5220,17 +5781,22 @@
       <c r="G116" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5267,12 +5833,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5304,17 +5875,22 @@
       <c r="G118" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5351,12 +5927,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5393,12 +5974,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5435,12 +6021,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5477,12 +6068,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5519,12 +6115,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5561,12 +6162,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5603,12 +6209,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5645,12 +6256,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5687,12 +6303,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5724,17 +6345,22 @@
       <c r="G128" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5771,12 +6397,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5813,12 +6444,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5855,12 +6491,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5897,12 +6538,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5939,12 +6585,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5981,12 +6632,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6023,12 +6679,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6060,17 +6721,22 @@
       <c r="G136" s="4" t="n">
         <v>-3.94</v>
       </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6107,12 +6773,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6149,12 +6820,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6186,17 +6862,22 @@
       <c r="G139" s="4" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6233,12 +6914,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6275,12 +6961,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6317,12 +7008,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6359,12 +7055,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6396,17 +7097,22 @@
       <c r="G144" s="4" t="n">
         <v>-6.47</v>
       </c>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6443,12 +7149,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6480,17 +7191,22 @@
       <c r="G146" s="4" t="n">
         <v>-6.55</v>
       </c>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6527,12 +7243,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6569,12 +7290,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6611,12 +7337,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6653,12 +7384,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6695,12 +7431,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6732,17 +7473,22 @@
       <c r="G152" s="4" t="n">
         <v>-4.92</v>
       </c>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6774,17 +7520,22 @@
       <c r="G153" s="4" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H153" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6821,12 +7572,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6863,12 +7619,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6900,17 +7661,22 @@
       <c r="G156" s="4" t="n">
         <v>-2.34</v>
       </c>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6947,12 +7713,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6989,12 +7760,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7031,12 +7807,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7073,12 +7854,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7110,17 +7896,22 @@
       <c r="G161" s="4" t="n">
         <v>-4.05</v>
       </c>
-      <c r="H161" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7157,12 +7948,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7199,12 +7995,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7241,12 +8042,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7283,12 +8089,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7325,12 +8136,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7362,17 +8178,22 @@
       <c r="G167" s="4" t="n">
         <v>-0.52</v>
       </c>
-      <c r="H167" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7409,12 +8230,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7451,12 +8277,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7493,12 +8324,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7530,17 +8366,22 @@
       <c r="G171" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7577,12 +8418,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7614,17 +8460,22 @@
       <c r="G173" s="4" t="n">
         <v>-3.06</v>
       </c>
-      <c r="H173" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7661,12 +8512,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7703,12 +8559,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7740,17 +8601,22 @@
       <c r="G176" s="4" t="n">
         <v>-1.88</v>
       </c>
-      <c r="H176" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7782,17 +8648,22 @@
       <c r="G177" s="4" t="n">
         <v>-4.21</v>
       </c>
-      <c r="H177" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7829,12 +8700,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7871,12 +8747,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7908,17 +8789,22 @@
       <c r="G180" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7955,12 +8841,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7997,12 +8888,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8034,17 +8930,22 @@
       <c r="G183" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8081,12 +8982,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8123,12 +9029,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8160,17 +9071,22 @@
       <c r="G186" s="4" t="n">
         <v>-2.84</v>
       </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8202,17 +9118,22 @@
       <c r="G187" s="4" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="H187" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8249,12 +9170,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8286,17 +9212,22 @@
       <c r="G189" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8333,12 +9264,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8375,12 +9311,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8412,17 +9353,22 @@
       <c r="G192" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8459,12 +9405,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8501,12 +9452,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8543,12 +9499,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8585,12 +9546,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8622,17 +9588,22 @@
       <c r="G197" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H197" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8664,17 +9635,22 @@
       <c r="G198" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H198" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8711,12 +9687,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8753,12 +9734,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I200" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8795,12 +9781,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8837,12 +9828,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8879,12 +9875,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8916,17 +9917,22 @@
       <c r="G204" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8963,12 +9969,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9005,12 +10016,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9047,12 +10063,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9084,17 +10105,22 @@
       <c r="G208" s="4" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H208" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9131,12 +10157,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9173,12 +10204,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9215,12 +10251,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9257,12 +10298,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9299,12 +10345,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9341,12 +10392,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9378,17 +10434,22 @@
       <c r="G215" s="4" t="n">
         <v>-1.88</v>
       </c>
-      <c r="H215" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9425,12 +10486,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9462,17 +10528,22 @@
       <c r="G217" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H217" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9509,12 +10580,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9551,12 +10627,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9593,12 +10674,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9635,12 +10721,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9677,12 +10768,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9714,17 +10810,22 @@
       <c r="G223" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H223" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9761,12 +10862,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9803,12 +10909,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9845,12 +10956,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9887,12 +11003,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9924,17 +11045,22 @@
       <c r="G228" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H228" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -9966,17 +11092,22 @@
       <c r="G229" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H229" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10013,12 +11144,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I230" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10055,12 +11191,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10097,12 +11238,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I232" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10139,12 +11285,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10181,12 +11332,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I234" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10218,17 +11374,22 @@
       <c r="G235" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H235" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I235" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10265,12 +11426,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I236" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10307,12 +11473,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10349,12 +11520,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I238" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10386,17 +11562,22 @@
       <c r="G239" s="4" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H239" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10433,12 +11614,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I240" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10475,12 +11661,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I241" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10517,12 +11708,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10559,12 +11755,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10601,12 +11802,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I244" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10643,12 +11849,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I245" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10680,17 +11891,22 @@
       <c r="G246" s="4" t="n">
         <v>-1.88</v>
       </c>
-      <c r="H246" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H246" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I246" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10727,12 +11943,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I247" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10764,17 +11985,22 @@
       <c r="G248" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H248" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I248" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10811,12 +12037,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I249" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10853,12 +12084,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I250" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10895,12 +12131,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I251" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10937,12 +12178,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+      <c r="I252" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -10959,7 +12205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10969,9 +12215,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11001,7 +12248,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -11026,15 +12273,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
